--- a/Docs/tank_bazaar_pipeline_tracker.xlsx
+++ b/Docs/tank_bazaar_pipeline_tracker.xlsx
@@ -4781,12 +4781,16 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
+        </is>
+      </c>
       <c r="M58" t="n">
-        <v>18.96</v>
+        <v>19.03</v>
       </c>
       <c r="N58" t="n">
-        <v>72.84999999999999</v>
+        <v>72.92</v>
       </c>
       <c r="O58" t="n">
         <v>19.1</v>
@@ -4796,11 +4800,11 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>[["Mumbai Refinery", 18.96, 72.85], ["Santacruz (Mumbai Airport)", -46.44, -67.53], ["Santacruz (Mumbai Airport)", 19.1, 72.87]]</t>
+          <t>[["Mumbai Refinery, India (origin)", 19.03, 72.92], ["Santacruz, Mumbai Airport, India (terminus)", 19.1, 72.87]]</t>
         </is>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -6093,14 +6097,14 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>CORRECTION (this research pass): the previous 'Operational' status was factually wrong. The specific Surat-Paradip natural gas pipeline (1,724km, proposed to run Mora/Gujarat to IOCL's Paradip refinery via Jalgaon/Nagpur/Raipur/Bhubaneswar, licensed to GAIL in 2012) was formally TERMINATED by India's Petroleum and Natural Gas Regulatory Board in March 2018, with the regulator's own order stating ground progress after 6 years was 'nil' - GAIL's full performance bank guarantee (Rs 200 million) was encashed as a penalty. This project was never built and does not exist as physical infrastructure. LIKELY SOURCE OF THE ERROR: the previous entry's note ('Extension of the Urja Ganga project, connects to JHBDPL at the eastern end') appears to have conflated this cancelled project with the genuinely real, separate, and largely-complete Jagdishpur-Haldia-Bokaro-Dhamra Pipeline (JHBDPL/'Pradhan Mantri Urja Ganga') - a different GAIL project entirely, running West-to-East across northern India (Uttar Pradesh through Bihar/Jharkhand/Odisha/West Bengal, with a further Barauni-Guwahati extension to Assam), 97.6% laid and 96.6% commercially operational as of April 2025, which DOES genuinely reach Paradip refinery among its endpoints - but via a completely different route than the cancelled Gujarat-origin Surat-Paradip line. No route path added, since this project has no physical route to map.</t>
+          <t>CORRECTION (this research pass): the previous 'Operational' status was factually wrong. The specific Surat-Paradip natural gas pipeline (1,724km, proposed to run Mora/Gujarat to IOCL's Paradip refinery via Jalgaon/Nagpur/Raipur/Bhubaneswar, licensed to GAIL in 2012) was formally TERMINATED by India's Petroleum and Natural Gas Regulatory Board in March 2018, with the regulator's own order stating ground progress after 6 years was 'nil' - GAIL's full performance bank guarantee (Rs 200 million) was encashed as a penalty. This project was never built and does not exist as physical infrastructure. LIKELY SOURCE OF THE ERROR: the previous entry's note ('Extension of the Urja Ganga project, connects to JHBDPL at the eastern end') appears to have conflated this cancelled project with the genuinely real, separate, and largely-complete Jagdishpur-Haldia-Bokaro-Dhamra Pipeline (JHBDPL/'Pradhan Mantri Urja Ganga') - a different GAIL project entirely, running West-to-East across northern India (Uttar Pradesh through Bihar/Jharkhand/Odisha/West Bengal, with a further Barauni-Guwahati extension to Assam), 97.6% laid and 96.6% commercially operational as of April 2025, which DOES genuinely reach Paradip refinery among its endpoints - but via a completely different route than the cancelled Gujarat-origin Surat-Paradip line. No route path added, since this project has no physical route to map. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-26.6</v>
+        <v>21.17</v>
       </c>
       <c r="N76" t="n">
-        <v>150.3</v>
+        <v>72.83</v>
       </c>
       <c r="O76" t="n">
         <v>20.26</v>
@@ -6110,7 +6114,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>[["Surat, Gujarat", -26.6, 150.3], ["Paradip", 20.26, 86.68]]</t>
+          <t>[["Surat, Gujarat, India (origin)", 21.17, 72.83], ["Paradip, Odisha, India (terminus - never built, cancelled 2018)", 20.26, 86.68]]</t>
         </is>
       </c>
       <c r="R76" t="n">
@@ -12921,28 +12925,28 @@
       </c>
       <c r="L169" s="10" t="inlineStr">
         <is>
-          <t>.5 billion project sanctioned under Argentina's RIGI investment incentive regime (30 years of tax/customs/FX regulatory stability for qualifying projects) - one of the first major projects approved under this new framework, alongside TGS's separate 50M Perito Moreno compression project. 36-inch pipeline, designed for a baseline 13 million m3/day to the La Carlota node. Intended to free up capacity on the existing Mercedes-Cardales interconnection ring between the TGS and TGN networks by giving incremental Vaca Muerta gas its own dedicated route north, rather than competing with existing Litoral-region supply.</t>
+          <t>.5 billion project sanctioned under Argentina's RIGI investment incentive regime (30 years of tax/customs/FX regulatory stability for qualifying projects) - one of the first major projects approved under this new framework, alongside TGS's separate 50M Perito Moreno compression project. 36-inch pipeline, designed for a baseline 13 million m3/day to the La Carlota node. Intended to free up capacity on the existing Mercedes-Cardales interconnection ring between the TGS and TGN networks by giving incremental Vaca Muerta gas its own dedicated route north, rather than competing with existing Litoral-region supply. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M169" t="n">
-        <v>-38.42738</v>
+        <v>-38.4274</v>
       </c>
       <c r="N169" t="n">
-        <v>-68.54749200000001</v>
+        <v>-68.5475</v>
       </c>
       <c r="O169" t="n">
-        <v>10.42</v>
+        <v>-33.433</v>
       </c>
       <c r="P169" t="n">
-        <v>122.93</v>
+        <v>-63.3</v>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>[["Tratayen, Neuquen Province (Vaca Muerta)", -38.4274, -68.5475], ["La Carlota", 10.66, 122.95], ["La Carlota, Cordoba Province (feeding onward into the Gasoducto Norte system)", 10.42, 122.93]]</t>
+          <t>[["Tratayen, Neuquen Province, Argentina (origin)", -38.4274, -68.5475], ["La Carlota, Cordoba, Argentina (terminus)", -33.433, -63.3]]</t>
         </is>
       </c>
       <c r="R169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
@@ -12993,24 +12997,24 @@
       </c>
       <c r="L170" s="10" t="inlineStr">
         <is>
-          <t>Inaugurated November 2024 - designed specifically to feed Vaca Muerta-origin gas into the Gasoducto Norte system, marking an early concrete step in reducing Argentina's reliance on Bolivian gas imports ahead of the larger Tratayen-La Carlota and GPNK expansion projects.</t>
+          <t>Inaugurated November 2024 - designed specifically to feed Vaca Muerta-origin gas into the Gasoducto Norte system, marking an early concrete step in reducing Argentina's reliance on Bolivian gas imports ahead of the larger Tratayen-La Carlota and GPNK expansion projects. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error ('La Carlota' exists in Argentina, Spain, AND the Philippines - a genuine place-name ambiguity) that caused the route to render across oceans incorrectly. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M170" t="n">
-        <v>10.42</v>
+        <v>-33.433</v>
       </c>
       <c r="N170" t="n">
-        <v>122.93</v>
+        <v>-63.3</v>
       </c>
       <c r="O170" t="n">
-        <v>-32.62</v>
+        <v>-32.286</v>
       </c>
       <c r="P170" t="n">
-        <v>-63.48</v>
+        <v>-63.354</v>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>[["La Carlota, Cordoba Province", 10.42, 122.93], ["Tio Pujio (feeding into Gasoducto Norte)", -32.62, -63.48]]</t>
+          <t>[["La Carlota, Cordoba, Argentina (origin)", -33.433, -63.3], ["Tio Pujio, Cordoba, Argentina (terminus)", -32.286, -63.354]]</t>
         </is>
       </c>
       <c r="R170" t="n">
@@ -13065,24 +13069,24 @@
       </c>
       <c r="L171" s="10" t="inlineStr">
         <is>
-          <t>Argentina's largest private oil transport infrastructure project in decades. Two phases: Loma Campana-Allen (~128km, 20/30-inch) and Allen-Punta Colorada (437km, 30-inch, initially paralleling the Oldelval Oil Pipeline before turning south). Cost .5-3 billion+, including a  billion syndicated loan from 14 international banks (Citi, JPMorgan, Deutsche Bank among them). Benefits from President Milei's RIGI investment incentive regime. Initial capacity 180,000 bpd (Dec 2026), scaling to 390,000 bpd (H2 2027), with design scalability to 550,000-720,000 bpd. Punta Colorada terminal will include a single-point mooring buoy capable of loading VLCCs, enabling direct export to Europe/Asia without transiting the Strait of Hormuz or Suez Canal. Shell and Chevron joined as shareholders after the project's initial formation. Also intended to open a Pacific/Chile export route.</t>
+          <t>Argentina's largest private oil transport infrastructure project in decades. Two phases: Loma Campana-Allen (~128km, 20/30-inch) and Allen-Punta Colorada (437km, 30-inch, initially paralleling the Oldelval Oil Pipeline before turning south). Cost .5-3 billion+, including a  billion syndicated loan from 14 international banks (Citi, JPMorgan, Deutsche Bank among them). Benefits from President Milei's RIGI investment incentive regime. Initial capacity 180,000 bpd (Dec 2026), scaling to 390,000 bpd (H2 2027), with design scalability to 550,000-720,000 bpd. Punta Colorada terminal will include a single-point mooring buoy capable of loading VLCCs, enabling direct export to Europe/Asia without transiting the Strait of Hormuz or Suez Canal. Shell and Chevron joined as shareholders after the project's initial formation. Also intended to open a Pacific/Chile export route. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M171" t="n">
-        <v>-34.17</v>
+        <v>-38.17</v>
       </c>
       <c r="N171" t="n">
-        <v>-58.96</v>
+        <v>-68.95999999999999</v>
       </c>
       <c r="O171" t="n">
-        <v>30.45</v>
+        <v>-41.02</v>
       </c>
       <c r="P171" t="n">
-        <v>-91.20999999999999</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>[["Loma Campana treatment plant, near Anelo, Neuquen Province (Vaca Muerta)", -34.17, -58.96], ["Allen", 30.45, -91.21], ["Rio Negro (Atlantic coast)", -39.0292, -65.4058]]</t>
+          <t>[["Loma Campana, near Anelo, Neuquen Province, Argentina (origin)", -38.17, -68.96], ["Allen, Rio Negro, Argentina (pumping station)", -38.98, -67.81], ["Punta Colorada, Golfo San Matias, Rio Negro, Argentina (terminus)", -41.02, -64.9]]</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -13137,7 +13141,7 @@
       </c>
       <c r="L172" s="10" t="inlineStr">
         <is>
-          <t>24-inch diameter. Adds ~74,000 m3/d (~465,000 bpd) of takeaway capacity specifically from Vaca Muerta's Northern Hub. Part of a coordinated bn+ combined expansion across Oldelval (crude) and TGS (gas/NGLs) aimed at eliminating Vaca Muerta's evacuation bottleneck before 2027.</t>
+          <t>24-inch diameter. Adds ~74,000 m3/d (~465,000 bpd) of takeaway capacity specifically from Vaca Muerta's Northern Hub. Part of a coordinated bn+ combined expansion across Oldelval (crude) and TGS (gas/NGLs) aimed at eliminating Vaca Muerta's evacuation bottleneck before 2027. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -13147,14 +13151,14 @@
         <v>-69.05</v>
       </c>
       <c r="O172" t="n">
-        <v>30.45</v>
+        <v>-38.98</v>
       </c>
       <c r="P172" t="n">
-        <v>-91.20999999999999</v>
+        <v>-67.81</v>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>[["Auca Mahuida pumping station, northern Neuquen Province (Vaca Muerta Northern Hub)", -37.7, -69.05], ["Allen", 30.45, -91.21]]</t>
+          <t>[["Auca Mahuida pumping station, northern Neuquen Province, Argentina (origin)", -37.7, -69.05], ["Allen, Rio Negro, Argentina (terminus)", -38.98, -67.81]]</t>
         </is>
       </c>
       <c r="R172" t="n">
@@ -15457,7 +15461,7 @@
       </c>
       <c r="L205" s="10" t="inlineStr">
         <is>
-          <t>GENUINELY NOTABLE FLOW REVERSAL: operation of the pipeline ceased in October 2021 amid the rupture of Algeria-Morocco diplomatic relations (Algeria refused to renew the transit/supply arrangement through Moroccan territory) - a case where geopolitics directly severed a two-decade energy relationship. In June 2022, a portion of the SAME physical pipeline was reversed to instead send gas FROM Spain TO Morocco, replacing the Algerian supply Morocco had lost. Structure: 515km Algeria-Morocco border section (Sonatrach); 522km Moroccan section (Metragaz JV); 45km offshore Strait of Gibraltar section (jointly owned Enagas/Transgas/Moroccan state); 269km Andalusian section; 269km Portuguese section; 270km Extremadura section. First proposed 1963 by French companies (originally envisioned extending to Strasbourg) but delayed for decades by the Western Sahara dispute preventing any Algeria-through-Morocco route.</t>
+          <t>GENUINELY NOTABLE FLOW REVERSAL: operation of the pipeline ceased in October 2021 amid the rupture of Algeria-Morocco diplomatic relations (Algeria refused to renew the transit/supply arrangement through Moroccan territory) - a case where geopolitics directly severed a two-decade energy relationship. In June 2022, a portion of the SAME physical pipeline was reversed to instead send gas FROM Spain TO Morocco, replacing the Algerian supply Morocco had lost. Structure: 515km Algeria-Morocco border section (Sonatrach); 522km Moroccan section (Metragaz JV); 45km offshore Strait of Gibraltar section (jointly owned Enagas/Transgas/Moroccan state); 269km Andalusian section; 269km Portuguese section; 270km Extremadura section. First proposed 1963 by French companies (originally envisioned extending to Strasbourg) but delayed for decades by the Western Sahara dispute preventing any Algeria-through-Morocco route. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -15467,18 +15471,18 @@
         <v>3.28</v>
       </c>
       <c r="O205" t="n">
-        <v>-31.42</v>
+        <v>37.667</v>
       </c>
       <c r="P205" t="n">
-        <v>-64.18000000000001</v>
+        <v>-4.933</v>
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>[["Hassi R'Mel gas field, Algeria", 32.93, 3.28], ["Andalusia", 37.2, -6.95], ["Cordoba, Andalusia, Spain, via Morocco and the Strait of Gibraltar (connecting onward to the Spanish and Portuguese gas grids)", -31.42, -64.18]]</t>
+          <t>[["Hassi R'Mel gas field, Algeria (origin)", 32.93, 3.28], ["Cordoba, Andalusia, Spain (terminus)", 37.667, -4.933]]</t>
         </is>
       </c>
       <c r="R205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -18715,24 +18719,24 @@
       </c>
       <c r="L255" s="10" t="inlineStr">
         <is>
-          <t>CONFIRMS A GENUINE NEAR-ABSENCE OF PIPELINE INFRASTRUCTURE, NOT A RESEARCH GAP: this ~1.5km flowline (oilfield wellhead to a moored FSO) is essentially the entirety of Cambodia's pipeline infrastructure. Cambodia has NO proven, extractable oil or gas reserves outside this single field, no refining capacity, and imports 100% of its refined petroleum products (chiefly from Vietnam, Singapore and Thailand). Apsara became Cambodia's first-ever oil production in late 2020 (~7,500 bpd from 5 wells), making it the 8th oil-producing ASEAN country, but KrisEnergy (the operator) entered financial difficulty and the field's continued production status is uncertain in sources reviewed here. Two long-discussed larger pipeline proposals - an offshore Gulf of Thailand-to-Preah Sihanouk crude line, and an onshore multi-province products pipeline across 7 provinces - remain at the feasibility-study stage (first studied 2016) with no confirmed construction. Cambodia Natural Gas Corp (CNGC, est. 2015) holds a 30-year gas development franchise and a 2020-2034 infrastructure plan, but no fossil gas production existed in Cambodia as of the most recent (2023) data reviewed.</t>
+          <t>CONFIRMS A GENUINE NEAR-ABSENCE OF PIPELINE INFRASTRUCTURE, NOT A RESEARCH GAP: this ~1.5km flowline (oilfield wellhead to a moored FSO) is essentially the entirety of Cambodia's pipeline infrastructure. Cambodia has NO proven, extractable oil or gas reserves outside this single field, no refining capacity, and imports 100% of its refined petroleum products (chiefly from Vietnam, Singapore and Thailand). Apsara became Cambodia's first-ever oil production in late 2020 (~7,500 bpd from 5 wells), making it the 8th oil-producing ASEAN country, but KrisEnergy (the operator) entered financial difficulty and the field's continued production status is uncertain in sources reviewed here. Two long-discussed larger pipeline proposals - an offshore Gulf of Thailand-to-Preah Sihanouk crude line, and an onshore multi-province products pipeline across 7 provinces - remain at the feasibility-study stage (first studied 2016) with no confirmed construction. Cambodia Natural Gas Corp (CNGC, est. 2015) holds a 30-year gas development franchise and a 2020-2034 infrastructure plan, but no fossil gas production existed in Cambodia as of the most recent (2023) data reviewed. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M255" t="n">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="N255" t="n">
         <v>103.9</v>
       </c>
       <c r="O255" t="n">
-        <v>58.01</v>
+        <v>10.51</v>
       </c>
       <c r="P255" t="n">
-        <v>56.23</v>
+        <v>103.91</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>[["Apsara oilfield, offshore Block A, Khmer Basin, Gulf of Thailand (~130km off Cambodia's west coast)", 13.2, 103.9], ["A permanently-moored floating storage and offloading (FSO) vessel at the same offshore location", 58.01, 56.23]]</t>
+          <t>[["Apsara oilfield, offshore Block A, Khmer Basin, Cambodia (origin)", 10.5, 103.9], ["Moored FSO vessel, same offshore location (terminus)", 10.51, 103.91]]</t>
         </is>
       </c>
       <c r="R255" t="n">
@@ -19787,28 +19791,28 @@
       </c>
       <c r="L272" s="11" t="inlineStr">
         <is>
-          <t>450,000 bpd design capacity but transported only ~150,000 bpd on average in 2022 (vs. SOTE's 320,000 bpd) - reflecting the Andean region's broader crude production decline. Carries heavier Napo grade crude (19 degree API) than SOTE's medium Oriente grade. Built before an environmental impact assessment was even completed - cited by Conservation International as 'unexpectedly common' among multilateral-development-bank-financed pipeline projects in this region (the same criticism applies to this registry's Peru/Camisea and Panama/Trans-Panama entries). Also ruptured in the same April 2020 erosion event as SOTE, and again in January 2022 (falling rocks), contaminating over 5 acres of Cayambe-Coca National Park. GENUINELY NOTABLE CURRENT DEVELOPMENT: given both Ecuadorian pipelines now run well under capacity, OCP has begun a cross-border arrangement transporting ~15,000 bpd of Colombian crude (loaded at the Nueva Loja terminal) and is in active pilot testing to do the same for Peruvian crude via the Napo River - Peru currently evacuates that production via a 45-day Amazon River barge journey, so pipeline access would be a significant logistics improvement if the pilot succeeds.</t>
+          <t>450,000 bpd design capacity but transported only ~150,000 bpd on average in 2022 (vs. SOTE's 320,000 bpd) - reflecting the Andean region's broader crude production decline. Carries heavier Napo grade crude (19 degree API) than SOTE's medium Oriente grade. Built before an environmental impact assessment was even completed - cited by Conservation International as 'unexpectedly common' among multilateral-development-bank-financed pipeline projects in this region (the same criticism applies to this registry's Peru/Camisea and Panama/Trans-Panama entries). Also ruptured in the same April 2020 erosion event as SOTE, and again in January 2022 (falling rocks), contaminating over 5 acres of Cayambe-Coca National Park. GENUINELY NOTABLE CURRENT DEVELOPMENT: given both Ecuadorian pipelines now run well under capacity, OCP has begun a cross-border arrangement transporting ~15,000 bpd of Colombian crude (loaded at the Nueva Loja terminal) and is in active pilot testing to do the same for Peruvian crude via the Napo River - Peru currently evacuates that production via a 45-day Amazon River barge journey, so pipeline access would be a significant logistics improvement if the pilot succeeds. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M272" t="n">
-        <v>-4.2</v>
+        <v>0.09</v>
       </c>
       <c r="N272" t="n">
-        <v>-63.1</v>
+        <v>-76.87</v>
       </c>
       <c r="O272" t="n">
-        <v>27.2</v>
+        <v>0.98</v>
       </c>
       <c r="P272" t="n">
-        <v>-13.16</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>[["Amazonas Terminal, Lago Agrio (Nueva Loja), Sucumbios province", -4.2, -63.1], ["Esmeraldas", 0.98, -79.65], ["OCP Marine Terminal, Esmeraldas, Ecuador (Pacific coast, adjacent to the SOTE terminus)", 27.2, -13.16]]</t>
+          <t>[["Amazonas Terminal, Lago Agrio (Nueva Loja), Sucumbios, Ecuador (origin)", 0.09, -76.87], ["OCP Marine Terminal, Esmeraldas, Ecuador (terminus)", 0.98, -79.65]]</t>
         </is>
       </c>
       <c r="R272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -19861,24 +19865,24 @@
       </c>
       <c r="L273" s="10" t="inlineStr">
         <is>
-          <t>One of the largest and most economically significant energy projects in Peru's history (US$2.7bn cost), transforming Peru into a gas-rich nation with an estimated US$34bn in royalties expected over the project's 30-year duration. TWO parallel pipelines cross the Andes together: a natural gas line to Lima/Callao and a separate natural gas liquids line to Pisco (feeding Peru LNG, see this registry's existing Peru entry in the LNG-adjacent portion of this project). Notable infrastructure-investor ownership: Canada's public pension fund (CPPIB) holds the plurality stake - the same pattern already seen with UK's CATS/Kellas Midstream and Spain's CLH/Macquarie elsewhere in this registry. CURRENT EXPANSION PROPOSAL: TGP has submitted a US$1.81bn plan for a new 817km coastal pipeline (Humay to Ilo, with branches to Arequipa and Mollendo) specifically to extend gas access to southern Peru, tied to a request to extend TGP's concession by a decade (to 2044) - a genuinely current, unbuilt proposal reflecting the long-standing difficulty of financing southern Peru gas infrastructure. Peru also operates a distinctive 'virtual pipeline' system (LNG trucked from a coastal liquefaction point to underserved interior areas) as a lower-cost alternative to physical pipeline extension - a similar approach used to a lesser degree in Colombia, Spain and Bolivia.</t>
+          <t>One of the largest and most economically significant energy projects in Peru's history (US$2.7bn cost), transforming Peru into a gas-rich nation with an estimated US$34bn in royalties expected over the project's 30-year duration. TWO parallel pipelines cross the Andes together: a natural gas line to Lima/Callao and a separate natural gas liquids line to Pisco (feeding Peru LNG, see this registry's existing Peru entry in the LNG-adjacent portion of this project). Notable infrastructure-investor ownership: Canada's public pension fund (CPPIB) holds the plurality stake - the same pattern already seen with UK's CATS/Kellas Midstream and Spain's CLH/Macquarie elsewhere in this registry. CURRENT EXPANSION PROPOSAL: TGP has submitted a US$1.81bn plan for a new 817km coastal pipeline (Humay to Ilo, with branches to Arequipa and Mollendo) specifically to extend gas access to southern Peru, tied to a request to extend TGP's concession by a decade (to 2044) - a genuinely current, unbuilt proposal reflecting the long-standing difficulty of financing southern Peru gas infrastructure. Peru also operates a distinctive 'virtual pipeline' system (LNG trucked from a coastal liquefaction point to underserved interior areas) as a lower-cost alternative to physical pipeline extension - a similar approach used to a lesser degree in Colombia, Spain and Bolivia. COORDINATE CORRECTION: this pipeline's waypoints previously contained a wrong-country coordinate error (a real place-name ambiguity, e.g. 'La Carlota' exists in Argentina, Spain, AND the Philippines) that caused the route to render across oceans/continents incorrectly on the map. Verified and corrected against independent geographic sources.</t>
         </is>
       </c>
       <c r="M273" t="n">
-        <v>-52.5</v>
+        <v>-11.85</v>
       </c>
       <c r="N273" t="n">
-        <v>-68.8</v>
+        <v>-72.94</v>
       </c>
       <c r="O273" t="n">
-        <v>40.74</v>
+        <v>-12.05</v>
       </c>
       <c r="P273" t="n">
-        <v>-84.11</v>
+        <v>-77.05</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>[["Malvinas separation plant, Camisea gas fields, Cusco region, Peruvian Amazon (Blocks 88/56, discovered by Shell 1986)", -52.5, -68.8], ["Lurin/Lima and Callao (natural gas, via a ~714-730km pipeline) and Pisco (natural gas liquids, via a separate parallel line) - crossing Cusco, Ayacucho, Huancavelica, Ica and Lima regions", 40.74, -84.11]]</t>
+          <t>[["Malvinas plant, Cusco Region, Peru (origin - Camisea gas fields)", -11.85, -72.94], ["Lima/Callao, Peru (terminus)", -12.05, -77.05]]</t>
         </is>
       </c>
       <c r="R273" t="n">

--- a/Docs/tank_bazaar_pipeline_tracker.xlsx
+++ b/Docs/tank_bazaar_pipeline_tracker.xlsx
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.5</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Two parallel dedicated lines, MS+HSD ROUTE-PATH NOTE: path researched via HPCL's own official pipeline-operations page, confirming this is a short dedicated dual-pipe (16in HSD + 14in MS) dispatch-to-terminus line with no further named intermediate stations.</t>
+          <t>Two parallel dedicated lines, MS+HSD ROUTE-PATH NOTE: path researched via HPCL's own official pipeline-operations page, confirming this is a short dedicated dual-pipe (16in HSD + 14in MS) dispatch-to-terminus line with no further named intermediate stations. LENGTH CORRECTION: stated length (10km) was inconsistent with the real-world distance between Barwala and Hisar, Haryana (~48km) - the coordinates were correct, the length figure was not.</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>Design capacity 3.8 million tonnes/year. Reported overall system length varies (~1415-2040km) across sources depending on whether feeder/branch sections are included - flagged for a closer look in a future pass.</t>
+          <t>Design capacity 3.8 million tonnes/year. Reported overall system length varies (~1415-2040km) across sources depending on whether feeder/branch sections are included - flagged for a closer look in a future pass. SECOND COORDINATE CORRECTION PASS: found via a lower-threshold audit (this error was under the 6000km hop threshold used in the first pass) - fixed a stray/wrong waypoint or waypoint-ordering issue that caused an implausible route line on the map.</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -6387,18 +6387,18 @@
         <v>69.84999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>40.64</v>
+        <v>28.75</v>
       </c>
       <c r="P80" t="n">
-        <v>22.94</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>[["Jamnagar, Gujarat", 22.34, 69.85], ["Loni", 28.75, 77.29], ["Loni, near Delhi", 40.64, 22.94]]</t>
+          <t>[["Jamnagar, Gujarat, India (origin)", 22.34, 69.85], ["Loni, near Delhi, India (terminus)", 28.75, 77.29]]</t>
         </is>
       </c>
       <c r="R80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>Multi-owner consortium: Phillips 66, Marathon, Sunoco Logistics (now part of Energy Transfer), Shell. Carries gasoline, diesel, fuel oil, jet fuel, and diluent.</t>
+          <t>Multi-owner consortium: Phillips 66, Marathon, Sunoco Logistics (now part of Energy Transfer), Shell. Carries gasoline, diesel, fuel oil, jet fuel, and diluent. SECOND COORDINATE CORRECTION PASS: found via a lower-threshold audit (this error was under the 6000km hop threshold used in the first pass) - fixed a stray/wrong waypoint or waypoint-ordering issue that caused an implausible route line on the map.</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -6765,18 +6765,18 @@
         <v>-93.94</v>
       </c>
       <c r="O85" t="n">
-        <v>41.6</v>
+        <v>37.93</v>
       </c>
       <c r="P85" t="n">
-        <v>-87.5</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>[["Port Arthur, Texas", 29.9, -93.94], ["Hammond", 41.6, -87.5], ["Indiana", 37.93, -87.9], ["Alberta)", 53.95, -113.11]]</t>
+          <t>[["Port Arthur, Texas, USA (origin)", 29.9, -93.94], ["Hammond, Indiana, USA area", 41.6, -87.5], ["Kankakee County, Illinois, USA (terminus - connects onward to Kinder Morgan's separate Cochin Pipeline toward Fort Saskatchewan, Alberta, not part of Explorer's own route)", 37.93, -87.9]]</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>China's first direct crude oil import pipeline, built in stages from 1997 agreement. 50/50 JV between CNPC and KazMunayGas.</t>
+          <t>China's first direct crude oil import pipeline, built in stages from 1997 agreement. 50/50 JV between CNPC and KazMunayGas. SECOND COORDINATE CORRECTION PASS: found via a lower-threshold audit (this error was under the 6000km hop threshold used in the first pass) - fixed a stray/wrong waypoint or waypoint-ordering issue that caused an implausible route line on the map.</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -8461,14 +8461,14 @@
         <v>51.88</v>
       </c>
       <c r="O107" t="n">
-        <v>45.18</v>
+        <v>41.73</v>
       </c>
       <c r="P107" t="n">
-        <v>82.56999999999999</v>
+        <v>86.13</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>[["Atyrau, Kazakhstan (already a TankBazaar facility, id 199)", 47.12, 51.88], ["Xinjiang", 41.73, 86.13], ["Alashankou, Xinjiang, China", 45.18, 82.57]]</t>
+          <t>[["Atyrau, Kazakhstan (origin)", 47.12, 51.88], ["Kazakhstan-China border area (intermediate)", 45.18, 82.57], ["Alashankou, Xinjiang, China (terminus)", 41.73, 86.13]]</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="L219" s="10" t="inlineStr">
         <is>
-          <t>28-inch diameter. One of two trunklines from the Grissik hub (South Sumatra gas fields), splitting at Sakernan - this branch runs north to Duri, the other (see separate row) runs to Singapore/Batam. Genuinely multinational ownership consortium spanning Indonesian, US, Malaysian, Chinese and Spanish state/major-company interests in one pipeline entity.</t>
+          <t>28-inch diameter. One of two trunklines from the Grissik hub (South Sumatra gas fields), splitting at Sakernan - this branch runs north to Duri, the other (see separate row) runs to Singapore/Batam. Genuinely multinational ownership consortium spanning Indonesian, US, Malaysian, Chinese and Spanish state/major-company interests in one pipeline entity. SECOND COORDINATE CORRECTION PASS: found via a lower-threshold audit (this error was under the 6000km hop threshold used in the first pass) - fixed a stray/wrong waypoint or waypoint-ordering issue that caused an implausible route line on the map.</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -16387,14 +16387,14 @@
         <v>102.15</v>
       </c>
       <c r="O219" t="n">
-        <v>13.3</v>
+        <v>1.27</v>
       </c>
       <c r="P219" t="n">
-        <v>74.75</v>
+        <v>101.35</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>[["Grissik gas plant, South Sumatra, Indonesia", -1.85, 102.15], ["Duri, Riau Province, Central Sumatra (feeding Chevron's giant Duri heavy-oil field steamflood operations)", 13.3, 74.75]]</t>
+          <t>[["Grissik gas plant, South Sumatra, Indonesia (origin)", -1.85, 102.15], ["Duri, Riau Province, Sumatra, Indonesia (terminus)", 1.27, 101.35]]</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -19941,14 +19941,14 @@
       </c>
       <c r="L274" s="10" t="inlineStr">
         <is>
-          <t>Bolivia's SECOND cross-border gas export pipeline (alongside the much larger GASBOL line to Brazil, already in this registry). 24-inch diameter, one of the oldest pipelines in this entire registry's South American section - signed 1968, built 1970-72, financed partly by the World Bank. Feeds directly into Argentina's Gasoducto Norte system, meaning Bolivian gas supply is a real, structural part of the same Argentine network now being reversed to instead carry Vaca Muerta shale gas north (see this registry's detailed Argentina entries) - Bolivia's exports via Yabog have been in long-term decline as both Bolivian production falls and Argentina develops its own alternative supply.</t>
+          <t>Bolivia's SECOND cross-border gas export pipeline (alongside the much larger GASBOL line to Brazil, already in this registry). 24-inch diameter, one of the oldest pipelines in this entire registry's South American section - signed 1968, built 1970-72, financed partly by the World Bank. Feeds directly into Argentina's Gasoducto Norte system, meaning Bolivian gas supply is a real, structural part of the same Argentine network now being reversed to instead carry Vaca Muerta shale gas north (see this registry's detailed Argentina entries) - Bolivia's exports via Yabog have been in long-term decline as both Bolivian production falls and Argentina develops its own alternative supply. COORDINATE CORRECTION: origin coordinate was wrong (landed in Uruguay/southern Brazil area instead of Santa Cruz Department, Bolivia).</t>
         </is>
       </c>
       <c r="M274" t="n">
-        <v>-32.03</v>
+        <v>-17.8</v>
       </c>
       <c r="N274" t="n">
-        <v>-52.1</v>
+        <v>-63.3</v>
       </c>
       <c r="O274" t="n">
         <v>-22.63</v>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>[["Rio Grande, Santa Cruz de la Sierra, Bolivia", -32.03, -52.1], ["Campo Duran", -22.63, -63.75]]</t>
+          <t>[["Rio Grande, Santa Cruz Department, Bolivia (origin)", -17.8, -63.3], ["Campo Duran, Salta Province, Argentina (terminus)", -22.63, -63.75]]</t>
         </is>
       </c>
       <c r="R274" t="n">
@@ -20447,28 +20447,28 @@
       </c>
       <c r="L282" s="11" t="inlineStr">
         <is>
-          <t>IRAQ'S OVERWHELMINGLY DOMINANT CRUDE EXPORT ROUTE - carrying the large majority of Iraq's oil exports via the offshore Al-Basra Oil Terminal (ABOT) and four associated Single Point Moorings (SPMs), fed by two 48-inch submarine pipelines (~75km) from the PS-1 pumping station, itself supplied from the southern Rumaila, West Qurna and Zubair fields. Current combined Gulf-terminal export capacity ~3.5 million bpd (1.25 million from ABOT, 2.25 million from the SPMs) - though ABOT's own capacity has been constrained for years by severely degraded connecting pipelines, with repair/upgrade works repeatedly delayed by financing problems. A third parallel 48-inch offshore pipeline began construction October 2025 specifically to add resilience. EXISTENTIAL FISCAL RISK, MADE CONCRETE BY THE 2026 IRAN WAR: Iraq derives approximately 90% of total government revenue from oil exports, and this single corridor runs through the Strait of Hormuz - during the 2026 US-Israel-Iran conflict, Hormuz disruption cut Basra exports by over 80%, forcing Iraq to lean on the Kirkuk-Ceyhan pipeline (see this registry's separate entry, itself now facing formal termination by Turkiye) as a partial workaround. Exports only began recovering from mid-April 2026 under a de facto Hormuz-transit exemption negotiated directly between Iraq and Iran - with roughly 17 million barrels of onshore inventory and 20+ million barrels of Gulf floating storage available to help restore flows over an estimated 3-month recovery window. Iraq's State Company for Oil Projects (SCOP) has reframed its long-planned Basra-Haditha pipeline expansion mandate from a routine infrastructure programme into what amounts to an emergency diversification response to this single-corridor vulnerability. A long-discussed alternative - a Basra-Aqaba pipeline to give Iraq Red Sea access via Jordan (up to 1 million bpd, Jordanian cabinet approval given 2018) - has seen little concrete progress despite years of discussion, precisely the kind of diversification this 2026 crisis has shown Iraq badly needs.</t>
+          <t>IRAQ'S OVERWHELMINGLY DOMINANT CRUDE EXPORT ROUTE - carrying the large majority of Iraq's oil exports via the offshore Al-Basra Oil Terminal (ABOT) and four associated Single Point Moorings (SPMs), fed by two 48-inch submarine pipelines (~75km) from the PS-1 pumping station, itself supplied from the southern Rumaila, West Qurna and Zubair fields. Current combined Gulf-terminal export capacity ~3.5 million bpd (1.25 million from ABOT, 2.25 million from the SPMs) - though ABOT's own capacity has been constrained for years by severely degraded connecting pipelines, with repair/upgrade works repeatedly delayed by financing problems. A third parallel 48-inch offshore pipeline began construction October 2025 specifically to add resilience. EXISTENTIAL FISCAL RISK, MADE CONCRETE BY THE 2026 IRAN WAR: Iraq derives approximately 90% of total government revenue from oil exports, and this single corridor runs through the Strait of Hormuz - during the 2026 US-Israel-Iran conflict, Hormuz disruption cut Basra exports by over 80%, forcing Iraq to lean on the Kirkuk-Ceyhan pipeline (see this registry's separate entry, itself now facing formal termination by Turkiye) as a partial workaround. Exports only began recovering from mid-April 2026 under a de facto Hormuz-transit exemption negotiated directly between Iraq and Iran - with roughly 17 million barrels of onshore inventory and 20+ million barrels of Gulf floating storage available to help restore flows over an estimated 3-month recovery window. Iraq's State Company for Oil Projects (SCOP) has reframed its long-planned Basra-Haditha pipeline expansion mandate from a routine infrastructure programme into what amounts to an emergency diversification response to this single-corridor vulnerability. A long-discussed alternative - a Basra-Aqaba pipeline to give Iraq Red Sea access via Jordan (up to 1 million bpd, Jordanian cabinet approval given 2018) - has seen little concrete progress despite years of discussion, precisely the kind of diversification this 2026 crisis has shown Iraq badly needs. SECOND COORDINATE CORRECTION PASS: found via a lower-threshold audit (this error was under the 6000km hop threshold used in the first pass) - fixed a stray/wrong waypoint or waypoint-ordering issue that caused an implausible route line on the map.</t>
         </is>
       </c>
       <c r="M282" t="n">
-        <v>63.05</v>
+        <v>30.05</v>
       </c>
       <c r="N282" t="n">
-        <v>75.3</v>
+        <v>47.8</v>
       </c>
       <c r="O282" t="n">
-        <v>30.05</v>
+        <v>29.7</v>
       </c>
       <c r="P282" t="n">
-        <v>47.8</v>
+        <v>48.8</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>[["PS-1 pumping station, Basra governorate, Iraq (fed by the Rumaila, West Qurna and Zubair fields)", 63.05, 75.3], ["Persian Gulf", 26.9, 52.2], ["Al-Basra Oil Terminal (ABOT), offshore Al-Faw Peninsula, Persian Gulf, plus associated Single Point Moorings", 30.05, 47.8]]</t>
+          <t>[["PS-1 pumping station, Basra governorate, Iraq (origin)", 30.05, 47.8], ["Al-Basra Oil Terminal (ABOT), offshore Al-Faw Peninsula, Iraq (terminus)", 29.7, 48.8]]</t>
         </is>
       </c>
       <c r="R282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -26747,7 +26747,7 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>28</v>
+        <v>247</v>
       </c>
       <c r="H373" t="n">
         <v>54</v>
@@ -26764,7 +26764,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>ROUTE-PATH NOTE: added via Phillips 66 Partners LP's own SEC 10-K filings (precise length/capacity tables). Wholly owned crude gathering, associated with Sweeny refinery. Distinct from Kinder Morgan's separately-named Eagle Ford Midstream gas system already in this tracker.</t>
+          <t>ROUTE-PATH NOTE: added via Phillips 66 Partners LP's own SEC 10-K filings (precise length/capacity tables). Wholly owned crude gathering, associated with Sweeny refinery. Distinct from Kinder Morgan's separately-named Eagle Ford Midstream gas system already in this tracker. LENGTH CORRECTION: the original 28 figure was very likely the pipe's 28-inch diameter mistakenly recorded as its length in km - corrected to the real-world distance (~247km) between the Eagle Ford shale region and Sweeny, Texas.</t>
         </is>
       </c>
       <c r="M373" t="n">
@@ -29970,7 +29970,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>ROUTE-PATH NOTE: added via Enbridge's own official Energy Infrastructure Assets factsheet. 4 pipelines: Link (Lambton County), Rockcliffe and Orleans (Ottawa), Cornwall (to northern New York State border).</t>
+          <t>ROUTE-PATH NOTE: added via Enbridge's own official Energy Infrastructure Assets factsheet. 4 pipelines: Link (Lambton County), Rockcliffe and Orleans (Ottawa), Cornwall (to northern New York State border). ROUTE CORRECTION: this system is genuinely 4 separate short local segments in different parts of Ontario (Lambton County, Ottawa x2, Cornwall), not one continuous pipeline - the previous 2-point path incorrectly drew one long line across the whole province. Simplified to represent only its primary named segment (Link, Lambton County) rather than a misleading long line.</t>
         </is>
       </c>
       <c r="M417" t="n">
@@ -29980,14 +29980,14 @@
         <v>-82.3</v>
       </c>
       <c r="O417" t="n">
-        <v>45.02</v>
+        <v>42.95</v>
       </c>
       <c r="P417" t="n">
-        <v>-74.73</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t>[["Lambton County, Ontario, Canada (Link Pipeline origin)", 42.9, -82.3], ["Cornwall, Ontario, Canada (terminus, near NY border)", 45.02, -74.73]]</t>
+          <t>[["Lambton County, Ontario, Canada (Link segment origin)", 42.9, -82.3], ["Sarnia area, Lambton County, Ontario, Canada (Tecumseh storage, Link segment terminus)", 42.95, -82.35]]</t>
         </is>
       </c>
       <c r="R417" t="n">
